--- a/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E71B2CD-E696-4D6E-84E8-574B4C94255D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58CE348D-8DD9-49EB-BEB8-0B20F88C987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1050,7 +1050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32BCD5B-D807-466A-8E71-EDA74F20DC73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057304A3-C40C-4AD3-A090-C573E007C1F6}">
   <dimension ref="B9:L44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58CE348D-8DD9-49EB-BEB8-0B20F88C987E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7933C9A8-00F1-4891-A31D-07B1D11DD13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1050,7 +1050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{057304A3-C40C-4AD3-A090-C573E007C1F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F86B2A8-DA69-4CA7-988C-880842FAD94E}">
   <dimension ref="B9:L44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72C92863-E5F4-494F-B249-0423320E1E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F309FDC-7A18-481C-80B7-84DDD7590A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="122">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -981,7 +981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2F6E750-205E-48B2-B9D8-ACFACEC285F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08520AEE-B062-4957-9D77-D9D557A72454}">
   <dimension ref="B9:L44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10581,6 +10581,12 @@
       <c r="B553">
         <v>2018</v>
       </c>
+      <c r="C553" t="s">
+        <v>60</v>
+      </c>
+      <c r="D553">
+        <v>1.962</v>
+      </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
@@ -10589,6 +10595,12 @@
       <c r="B554">
         <v>2019</v>
       </c>
+      <c r="C554" t="s">
+        <v>60</v>
+      </c>
+      <c r="D554">
+        <v>3.302</v>
+      </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
@@ -10597,6 +10609,12 @@
       <c r="B555">
         <v>2020</v>
       </c>
+      <c r="C555" t="s">
+        <v>60</v>
+      </c>
+      <c r="D555">
+        <v>5.1020000000000003</v>
+      </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
@@ -10605,6 +10623,12 @@
       <c r="B556">
         <v>2021</v>
       </c>
+      <c r="C556" t="s">
+        <v>60</v>
+      </c>
+      <c r="D556">
+        <v>7.1550000000000002</v>
+      </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
@@ -10613,6 +10637,12 @@
       <c r="B557">
         <v>2022</v>
       </c>
+      <c r="C557" t="s">
+        <v>60</v>
+      </c>
+      <c r="D557">
+        <v>113</v>
+      </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
@@ -10621,6 +10651,12 @@
       <c r="B558">
         <v>2023</v>
       </c>
+      <c r="C558" t="s">
+        <v>60</v>
+      </c>
+      <c r="D558">
+        <v>319</v>
+      </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
@@ -10629,6 +10665,12 @@
       <c r="B559">
         <v>2024</v>
       </c>
+      <c r="C559" t="s">
+        <v>60</v>
+      </c>
+      <c r="D559">
+        <v>466</v>
+      </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
@@ -10637,389 +10679,683 @@
       <c r="B560">
         <v>2016</v>
       </c>
-    </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C560" t="s">
+        <v>60</v>
+      </c>
+      <c r="D560">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>9</v>
       </c>
       <c r="B561">
         <v>2017</v>
       </c>
-    </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C561" t="s">
+        <v>60</v>
+      </c>
+      <c r="D561">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>9</v>
       </c>
       <c r="B562">
         <v>2012</v>
       </c>
-    </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C562" t="s">
+        <v>59</v>
+      </c>
+      <c r="D562">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>9</v>
       </c>
       <c r="B563">
         <v>2013</v>
       </c>
-    </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C563" t="s">
+        <v>59</v>
+      </c>
+      <c r="D563">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>9</v>
       </c>
       <c r="B564">
         <v>2014</v>
       </c>
-    </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C564" t="s">
+        <v>59</v>
+      </c>
+      <c r="D564">
+        <v>9.9000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>9</v>
       </c>
       <c r="B565">
         <v>2015</v>
       </c>
-    </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C565" t="s">
+        <v>59</v>
+      </c>
+      <c r="D565">
+        <v>0.23499999999999999</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>9</v>
       </c>
       <c r="B566">
         <v>2016</v>
       </c>
-    </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C566" t="s">
+        <v>59</v>
+      </c>
+      <c r="D566">
+        <v>0.38200000000000001</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>9</v>
       </c>
       <c r="B567">
         <v>2017</v>
       </c>
-    </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C567" t="s">
+        <v>59</v>
+      </c>
+      <c r="D567">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>9</v>
       </c>
       <c r="B568">
         <v>2018</v>
       </c>
-    </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C568" t="s">
+        <v>59</v>
+      </c>
+      <c r="D568">
+        <v>1.2729999999999999</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>9</v>
       </c>
       <c r="B569">
         <v>2019</v>
       </c>
-    </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C569" t="s">
+        <v>59</v>
+      </c>
+      <c r="D569">
+        <v>3.137</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
         <v>9</v>
       </c>
       <c r="B570">
         <v>2020</v>
       </c>
-    </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C570" t="s">
+        <v>59</v>
+      </c>
+      <c r="D570">
+        <v>4.8470000000000004</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
         <v>9</v>
       </c>
       <c r="B571">
         <v>2021</v>
       </c>
-    </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C571" t="s">
+        <v>59</v>
+      </c>
+      <c r="D571">
+        <v>6.7969999999999997</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
         <v>9</v>
       </c>
       <c r="B572">
         <v>2022</v>
       </c>
-    </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C572" t="s">
+        <v>59</v>
+      </c>
+      <c r="D572">
+        <v>41.276000000000003</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
         <v>88</v>
       </c>
       <c r="B573">
         <v>2018</v>
       </c>
-    </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C573" t="s">
+        <v>60</v>
+      </c>
+      <c r="D573">
+        <v>78.171999999999997</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>88</v>
       </c>
       <c r="B574">
         <v>2019</v>
       </c>
-    </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C574" t="s">
+        <v>60</v>
+      </c>
+      <c r="D574">
+        <v>78.171999999999997</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>88</v>
       </c>
       <c r="B575">
         <v>2020</v>
       </c>
-    </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C575" t="s">
+        <v>60</v>
+      </c>
+      <c r="D575">
+        <v>78.171999999999997</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>88</v>
       </c>
       <c r="B576">
         <v>2021</v>
       </c>
-    </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C576" t="s">
+        <v>60</v>
+      </c>
+      <c r="D576">
+        <v>77.129000000000005</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>88</v>
       </c>
       <c r="B577">
         <v>2022</v>
       </c>
-    </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C577" t="s">
+        <v>60</v>
+      </c>
+      <c r="D577">
+        <v>82.426000000000002</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
         <v>88</v>
       </c>
       <c r="B578">
         <v>2023</v>
       </c>
-    </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C578" t="s">
+        <v>60</v>
+      </c>
+      <c r="D578">
+        <v>128.268</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>88</v>
       </c>
       <c r="B579">
         <v>2024</v>
       </c>
-    </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C579" t="s">
+        <v>60</v>
+      </c>
+      <c r="D579">
+        <v>128.268</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
         <v>88</v>
       </c>
       <c r="B580">
         <v>2011</v>
       </c>
-    </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C580" t="s">
+        <v>60</v>
+      </c>
+      <c r="D580">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
         <v>88</v>
       </c>
       <c r="B581">
         <v>2012</v>
       </c>
-    </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C581" t="s">
+        <v>60</v>
+      </c>
+      <c r="D581">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
         <v>88</v>
       </c>
       <c r="B582">
         <v>2013</v>
       </c>
-    </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C582" t="s">
+        <v>60</v>
+      </c>
+      <c r="D582">
+        <v>65.891999999999996</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
         <v>88</v>
       </c>
       <c r="B583">
         <v>2014</v>
       </c>
-    </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C583" t="s">
+        <v>60</v>
+      </c>
+      <c r="D583">
+        <v>68.915000000000006</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
         <v>88</v>
       </c>
       <c r="B584">
         <v>2015</v>
       </c>
-    </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C584" t="s">
+        <v>60</v>
+      </c>
+      <c r="D584">
+        <v>68.165000000000006</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
         <v>88</v>
       </c>
       <c r="B585">
         <v>2016</v>
       </c>
-    </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C585" t="s">
+        <v>60</v>
+      </c>
+      <c r="D585">
+        <v>69.905000000000001</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>88</v>
       </c>
       <c r="B586">
         <v>2017</v>
       </c>
-    </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C586" t="s">
+        <v>60</v>
+      </c>
+      <c r="D586">
+        <v>77.105000000000004</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>88</v>
       </c>
       <c r="B587">
         <v>2004</v>
       </c>
-    </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C587" t="s">
+        <v>60</v>
+      </c>
+      <c r="D587">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>88</v>
       </c>
       <c r="B588">
         <v>2005</v>
       </c>
-    </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C588" t="s">
+        <v>60</v>
+      </c>
+      <c r="D588">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>88</v>
       </c>
       <c r="B589">
         <v>2006</v>
       </c>
-    </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C589" t="s">
+        <v>60</v>
+      </c>
+      <c r="D589">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>88</v>
       </c>
       <c r="B590">
         <v>2007</v>
       </c>
-    </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C590" t="s">
+        <v>60</v>
+      </c>
+      <c r="D590">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
         <v>88</v>
       </c>
       <c r="B591">
         <v>2008</v>
       </c>
-    </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C591" t="s">
+        <v>60</v>
+      </c>
+      <c r="D591">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
         <v>88</v>
       </c>
       <c r="B592">
         <v>2009</v>
       </c>
-    </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C592" t="s">
+        <v>60</v>
+      </c>
+      <c r="D592">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
         <v>88</v>
       </c>
       <c r="B593">
         <v>2010</v>
       </c>
-    </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C593" t="s">
+        <v>60</v>
+      </c>
+      <c r="D593">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
         <v>88</v>
       </c>
       <c r="B594">
         <v>2000</v>
       </c>
-    </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C594" t="s">
+        <v>60</v>
+      </c>
+      <c r="D594">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
         <v>88</v>
       </c>
       <c r="B595">
         <v>2001</v>
       </c>
-    </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C595" t="s">
+        <v>60</v>
+      </c>
+      <c r="D595">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
         <v>88</v>
       </c>
       <c r="B596">
         <v>2002</v>
       </c>
-    </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C596" t="s">
+        <v>60</v>
+      </c>
+      <c r="D596">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
         <v>88</v>
       </c>
       <c r="B597">
         <v>2003</v>
       </c>
-    </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C597" t="s">
+        <v>60</v>
+      </c>
+      <c r="D597">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>88</v>
       </c>
       <c r="B598">
         <v>2002</v>
       </c>
-    </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C598" t="s">
+        <v>59</v>
+      </c>
+      <c r="D598">
+        <v>11.242000000000001</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>88</v>
       </c>
       <c r="B599">
         <v>2003</v>
       </c>
-    </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C599" t="s">
+        <v>59</v>
+      </c>
+      <c r="D599">
+        <v>48.445999999999998</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>88</v>
       </c>
       <c r="B600">
         <v>2004</v>
       </c>
-    </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C600" t="s">
+        <v>59</v>
+      </c>
+      <c r="D600">
+        <v>49.146999999999998</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
         <v>88</v>
       </c>
       <c r="B601">
         <v>2005</v>
       </c>
-    </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C601" t="s">
+        <v>59</v>
+      </c>
+      <c r="D601">
+        <v>46.853999999999999</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
         <v>88</v>
       </c>
       <c r="B602">
         <v>2006</v>
       </c>
-    </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C602" t="s">
+        <v>59</v>
+      </c>
+      <c r="D602">
+        <v>46.212000000000003</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>88</v>
       </c>
       <c r="B603">
         <v>2007</v>
       </c>
-    </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C603" t="s">
+        <v>59</v>
+      </c>
+      <c r="D603">
+        <v>52.929000000000002</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>88</v>
       </c>
       <c r="B604">
         <v>2008</v>
       </c>
-    </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C604" t="s">
+        <v>59</v>
+      </c>
+      <c r="D604">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
         <v>88</v>
       </c>
       <c r="B605">
         <v>2009</v>
       </c>
-    </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C605" t="s">
+        <v>59</v>
+      </c>
+      <c r="D605">
+        <v>50.088999999999999</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
         <v>88</v>
       </c>
       <c r="B606">
         <v>2010</v>
       </c>
-    </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C606" t="s">
+        <v>59</v>
+      </c>
+      <c r="D606">
+        <v>49.057000000000002</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>88</v>
       </c>
       <c r="B607">
         <v>2011</v>
       </c>
-    </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C607" t="s">
+        <v>59</v>
+      </c>
+      <c r="D607">
+        <v>70.894000000000005</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>88</v>
       </c>
       <c r="B608">
         <v>2012</v>
+      </c>
+      <c r="C608" t="s">
+        <v>59</v>
+      </c>
+      <c r="D608">
+        <v>114.26600000000001</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.45">
@@ -11029,6 +11365,12 @@
       <c r="B609">
         <v>2013</v>
       </c>
+      <c r="C609" t="s">
+        <v>59</v>
+      </c>
+      <c r="D609">
+        <v>120.05500000000001</v>
+      </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
@@ -11037,6 +11379,12 @@
       <c r="B610">
         <v>2014</v>
       </c>
+      <c r="C610" t="s">
+        <v>59</v>
+      </c>
+      <c r="D610">
+        <v>139.71199999999999</v>
+      </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
@@ -11045,6 +11393,12 @@
       <c r="B611">
         <v>2015</v>
       </c>
+      <c r="C611" t="s">
+        <v>59</v>
+      </c>
+      <c r="D611">
+        <v>147.13499999999999</v>
+      </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
@@ -11053,6 +11407,12 @@
       <c r="B612">
         <v>2016</v>
       </c>
+      <c r="C612" t="s">
+        <v>59</v>
+      </c>
+      <c r="D612">
+        <v>127.889</v>
+      </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
@@ -11061,6 +11421,12 @@
       <c r="B613">
         <v>2017</v>
       </c>
+      <c r="C613" t="s">
+        <v>59</v>
+      </c>
+      <c r="D613">
+        <v>150</v>
+      </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
@@ -11069,6 +11435,12 @@
       <c r="B614">
         <v>2018</v>
       </c>
+      <c r="C614" t="s">
+        <v>59</v>
+      </c>
+      <c r="D614">
+        <v>122.038</v>
+      </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
@@ -11077,6 +11449,12 @@
       <c r="B615">
         <v>2019</v>
       </c>
+      <c r="C615" t="s">
+        <v>59</v>
+      </c>
+      <c r="D615">
+        <v>153.999</v>
+      </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
@@ -11085,6 +11463,12 @@
       <c r="B616">
         <v>2020</v>
       </c>
+      <c r="C616" t="s">
+        <v>59</v>
+      </c>
+      <c r="D616">
+        <v>176.84200000000001</v>
+      </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
@@ -11093,6 +11477,12 @@
       <c r="B617">
         <v>2021</v>
       </c>
+      <c r="C617" t="s">
+        <v>59</v>
+      </c>
+      <c r="D617">
+        <v>141.43600000000001</v>
+      </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
@@ -11101,6 +11491,12 @@
       <c r="B618">
         <v>2022</v>
       </c>
+      <c r="C618" t="s">
+        <v>59</v>
+      </c>
+      <c r="D618">
+        <v>190.18299999999999</v>
+      </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
@@ -11109,6 +11505,12 @@
       <c r="B619">
         <v>2000</v>
       </c>
+      <c r="C619" t="s">
+        <v>59</v>
+      </c>
+      <c r="D619">
+        <v>4.4169999999999998</v>
+      </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
@@ -11116,6 +11518,12 @@
       </c>
       <c r="B620">
         <v>2001</v>
+      </c>
+      <c r="C620" t="s">
+        <v>59</v>
+      </c>
+      <c r="D620">
+        <v>3.4329999999999998</v>
       </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.45">

--- a/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F309FDC-7A18-481C-80B7-84DDD7590A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75F5DCD4-D813-46AB-B7E5-3CFA6CF5BD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -981,7 +981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08520AEE-B062-4957-9D77-D9D557A72454}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93AE951D-13B7-4AA6-873A-1879EF5FA926}">
   <dimension ref="B9:L44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_LVA/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75F5DCD4-D813-46AB-B7E5-3CFA6CF5BD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35F29857-00CD-4496-A966-16B7A3019186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -981,7 +981,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93AE951D-13B7-4AA6-873A-1879EF5FA926}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64972136-9540-42AF-B342-C81FCBB9A090}">
   <dimension ref="B9:L44"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
